--- a/output/reports/20260709_欠席分析報告書.xlsx
+++ b/output/reports/20260709_欠席分析報告書.xlsx
@@ -2508,7 +2508,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="B16" s="33" t="inlineStr">
         <is>
-          <t>AI予測では対象児童2名中2名で予測期間内の安定化が見込まれた。最も早い児童は約5か月後に安定すると予測された。今後も健康観察と、家庭と保育園・学校との情報共有を継続し、児童ごとの状況に応じた支援を行うことが望まれる。</t>
+          <t>AI予測では対象児童2名中2名で予測期間内の安定化が見込まれた。最も早い児童は約5か月後に安定すると予測された。今後も欠席傾向の確認と、家庭と保育園・学校との情報共有を継続し、児童ごとの状況に応じた支援を行うことが望まれる。</t>
         </is>
       </c>
       <c r="C16" s="34" t="n"/>

--- a/output/reports/20260709_欠席分析報告書.xlsx
+++ b/output/reports/20260709_欠席分析報告書.xlsx
@@ -2412,7 +2412,8 @@
     <row r="4" ht="15" customHeight="1">
       <c r="B4" s="33" t="inlineStr">
         <is>
-          <t>AIによる予測では、対象児童2名の平均欠席日数は約1.6日と推定された。全員が予測期間内に安定化すると予測され、今後も状況確認を継続することが望まれる。</t>
+          <t>AIによる予測では、対象児童2名の平均欠席日数は約1.6日と推定された。全員が予測期間内に安定化すると予測され、今後も状況確認を継続することが望まれる。
+また、学習データに対する予測精度（平均絶対誤差：MAE）は子供001：0.53日、子供002：0.39日であり、学習データの傾向を概ね再現できていることを確認した。</t>
         </is>
       </c>
       <c r="C4" s="34" t="n"/>

--- a/output/reports/20260709_欠席分析報告書.xlsx
+++ b/output/reports/20260709_欠席分析報告書.xlsx
@@ -2413,7 +2413,7 @@
       <c r="B4" s="33" t="inlineStr">
         <is>
           <t>AIによる予測では、対象児童2名の平均欠席日数は約1.6日と推定された。全員が予測期間内に安定化すると予測され、今後も状況確認を継続することが望まれる。
-また、学習データに対する予測精度（平均絶対誤差：MAE）は子供001：0.53日、子供002：0.39日であり、学習データの傾向を概ね再現できていることを確認した。</t>
+また、モデルの学習状況を確認するため、学習データに対する予測誤差（平均絶対誤差：MAE）を算出した。その結果、MAEは子供001：0.53日、子供002：0.39日であった。</t>
         </is>
       </c>
       <c r="C4" s="34" t="n"/>
